--- a/model_fitting/2010/model2_count_IRR.xlsx
+++ b/model_fitting/2010/model2_count_IRR.xlsx
@@ -555,7 +555,7 @@
         <v>1.026</v>
       </c>
       <c r="E6" t="n">
-        <v>0.7724</v>
+        <v>0.7727000000000001</v>
       </c>
       <c r="F6" t="inlineStr"/>
     </row>
@@ -675,7 +675,7 @@
         <v>1.676</v>
       </c>
       <c r="E12" t="n">
-        <v>0.7917999999999999</v>
+        <v>0.7917</v>
       </c>
       <c r="F12" t="inlineStr"/>
     </row>
@@ -715,7 +715,7 @@
         <v>1.335</v>
       </c>
       <c r="E14" t="n">
-        <v>0.5855</v>
+        <v>0.5856</v>
       </c>
       <c r="F14" t="inlineStr"/>
     </row>
@@ -795,7 +795,7 @@
         <v>1.002</v>
       </c>
       <c r="E18" t="n">
-        <v>0.2399</v>
+        <v>0.2404</v>
       </c>
       <c r="F18" t="inlineStr"/>
     </row>
@@ -839,7 +839,7 @@
         <v>1.261</v>
       </c>
       <c r="E20" t="n">
-        <v>0.9274</v>
+        <v>0.9275</v>
       </c>
       <c r="F20" t="inlineStr"/>
     </row>
